--- a/output/pdf_financials_xlsx/LECR.xlsx
+++ b/output/pdf_financials_xlsx/LECR.xlsx
@@ -2199,16 +2199,16 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>1.74692</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>1.74692</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>1.797343</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>1.83365</v>
       </c>
     </row>
     <row r="93">
@@ -2681,16 +2681,16 @@
         </is>
       </c>
       <c r="B118" s="3" t="n">
-        <v>0.555584</v>
+        <v>-2.553569</v>
       </c>
       <c r="C118" s="3" t="n">
-        <v>8.271882</v>
+        <v>6.662632</v>
       </c>
       <c r="D118" s="3" t="n">
-        <v>1.007128</v>
+        <v>0.879045</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>0.0435</v>
+        <v>-1.15284</v>
       </c>
     </row>
     <row r="119">
@@ -3428,7 +3428,11 @@
           <t>Share-based payment reserve (Note 7)</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E11" s="5" t="n">
         <v>1.74692</v>
       </c>
@@ -4006,7 +4010,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E28" s="5" t="n">
         <v>-3.109153</v>
       </c>

--- a/output/pdf_financials_xlsx/LECR.xlsx
+++ b/output/pdf_financials_xlsx/LECR.xlsx
@@ -639,13 +639,13 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.072213</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.15529</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.028984</v>
       </c>
       <c r="E12" s="3" t="n">
         <v>0</v>
@@ -944,13 +944,13 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.506506</v>
+        <v>-0.578719</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-8.142884</v>
+        <v>-8.298173999999999</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.10967</v>
+        <v>-0.138654</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>-1.769893</v>
@@ -982,13 +982,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.506506</v>
+        <v>-0.578719</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-8.142884</v>
+        <v>-8.298173999999999</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.10967</v>
+        <v>-0.138654</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>-1.769893</v>
@@ -1090,7 +1090,7 @@
         <v>2.543212</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>1.314363</v>
       </c>
     </row>
     <row r="35">
@@ -1128,7 +1128,7 @@
         <v>6.866741</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>3.441176</v>
+        <v>4.755539</v>
       </c>
     </row>
     <row r="37">
@@ -1356,7 +1356,7 @@
         <v>0.09546</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>1.329983</v>
+        <v>0.01562</v>
       </c>
     </row>
     <row r="49">
@@ -3124,7 +3124,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -5184,7 +5184,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -5388,7 +5388,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E67" s="5" t="n">

--- a/output/pdf_financials_xlsx/LECR.xlsx
+++ b/output/pdf_financials_xlsx/LECR.xlsx
@@ -4078,7 +4078,11 @@
           <t>Proceeds from shares issued</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E30" t="inlineStr">
         <is>
           <t>-</t>
